--- a/29_Fund_of_Funds/instances/public_hlpaf_2026.xlsx
+++ b/29_Fund_of_Funds/instances/public_hlpaf_2026.xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
     </row>

--- a/29_Fund_of_Funds/instances/public_hlpaf_2026.xlsx
+++ b/29_Fund_of_Funds/instances/public_hlpaf_2026.xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
     </row>

--- a/29_Fund_of_Funds/instances/public_hlpaf_2026.xlsx
+++ b/29_Fund_of_Funds/instances/public_hlpaf_2026.xlsx
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="C5" s="29" t="n">
-        <v>3621.4</v>
+        <v>3621.38</v>
       </c>
     </row>
     <row r="6">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="C6" s="29" t="n">
-        <v>1630.5</v>
+        <v>1630.474</v>
       </c>
     </row>
     <row r="7">
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>88.2</v>
+        <v>88.161</v>
       </c>
     </row>
     <row r="8">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="C10" s="29" t="n">
-        <v>735.3</v>
+        <v>735.347</v>
       </c>
     </row>
     <row r="11">
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>C5+C6-C7-C8-C9+C10</f>
+        <f>C5+C6-C7-IF(ISBLANK(C14),C8,C14)-C9+C10</f>
         <v/>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="C12" s="29" t="n">
-        <v>5785.7</v>
+        <v>5785.75</v>
       </c>
     </row>
     <row r="13">
@@ -3165,6 +3165,16 @@
       <c r="C13" s="10">
         <f>C11-C12</f>
         <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>- Disclosed net investment loss (supersedes modelled fee when sourced)</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>113.289</v>
       </c>
     </row>
     <row r="15">
